--- a/outputs/evaluation/architecture/validation/CF_M06/run_2/CF_M06_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/validation/CF_M06/run_2/CF_M06_arch_eval.xlsx
@@ -451,10 +451,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9286</v>
+        <v>0.8095</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7222</v>
+        <v>0.4722</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -469,13 +469,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9565</v>
+        <v>0.875</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7586000000000001</v>
+        <v>0.4828</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9592000000000001</v>
+        <v>0.9266</v>
       </c>
     </row>
     <row r="4">
@@ -485,13 +485,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6667</v>
+        <v>0.4286</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8841</v>
+        <v>0.8781</v>
       </c>
     </row>
     <row r="7">
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9231</v>
+        <v>0.8824</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -533,10 +533,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8636</v>
+        <v>0.6429</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8811</v>
+        <v>0.8223</v>
       </c>
     </row>
     <row r="10">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8846000000000001</v>
+        <v>0.8824</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2727</v>
+        <v>0.3</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -642,16 +642,16 @@
         <v>24</v>
       </c>
       <c r="C2" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9444</v>
+        <v>0.9167</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7083</v>
+        <v>0.4583</v>
       </c>
     </row>
     <row r="3">
@@ -664,16 +664,16 @@
         <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="4">
@@ -689,13 +689,13 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5714</v>
+        <v>0.4286</v>
       </c>
     </row>
   </sheetData>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9286</v>
+        <v>0.8095</v>
       </c>
     </row>
     <row r="9">
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7222</v>
+        <v>0.4722</v>
       </c>
     </row>
     <row r="10">
@@ -880,22 +880,22 @@
         <v>29</v>
       </c>
       <c r="C2" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D2" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E2" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F2" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G2" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="H2" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
@@ -905,25 +905,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" t="n">
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
@@ -936,22 +936,22 @@
         <v>36</v>
       </c>
       <c r="C4" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D4" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="E4" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F4" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G4" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="H4" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
@@ -964,22 +964,22 @@
         <v>29</v>
       </c>
       <c r="C5" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D5" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E5" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F5" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G5" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="H5" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
@@ -992,22 +992,22 @@
         <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D6" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="E6" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F6" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G6" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H6" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
@@ -1023,19 +1023,19 @@
         <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G7" t="n">
         <v>3</v>
       </c>
       <c r="H7" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
@@ -1063,7 +1063,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -1077,7 +1077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T27"/>
+  <dimension ref="A1:T18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1185,7 +1185,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AU_03</t>
+          <t>AU_04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>The layer that communicates with the user, displaying system data and collecting user input; in this case, the mobile application.</t>
+          <t>The layer that communicates with the user, displaying system data and collecting user input.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1225,7 +1225,7 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>AU_03</t>
+          <t>AU_04</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
@@ -1263,159 +1263,159 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AU_05</t>
+          <t>AU_15</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CF_M06_AU05</t>
+          <t>CF_M06_AU30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.8185</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Data Layer</t>
-        </is>
-      </c>
+        <v>0.8071</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>The layer that contains the information.</t>
+          <t>The application uses sockets to show content in real time from the server.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>['AU_04', 'AU_03']</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>AU_05</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Data</t>
-        </is>
-      </c>
+          <t>AU_15</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>presentation layer, waapiti platform</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>this is the layer that contains the information.</t>
+          <t>This functionality connects via socket [25] with the server and displays</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>CF_M06_P01</t>
+          <t>CF_M06_AU23, CF_M06_AU02</t>
         </is>
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
-          <t>CF_M06_AU05</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr"/>
+          <t>CF_M06_AU30</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>mobile application, waapiti server</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P_03</t>
+          <t>AU_06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CF_M06_P03</t>
+          <t>CF_M06_AU05</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.825</v>
+        <v>0.8185</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Observer</t>
+          <t>Data Layer</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>A design pattern to observe the state of an object in a program, reflected in the Flux architecture where stores act as subjects.</t>
+          <t>The layer that contains the information.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>['P_02']</t>
-        </is>
-      </c>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>P_03</t>
+          <t>AU_06</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Observer Pattern</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>The observer pattern is a design pattern for observing the state of an object in a program.</t>
+          <t>this is the layer that contains the information.</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>CF_M06_P02</t>
+          <t>CF_M06_P01</t>
         </is>
       </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
-          <t>CF_M06_P03</t>
+          <t>CF_M06_AU05</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -1423,12 +1423,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P_04</t>
+          <t>P_03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CF_M06_P04</t>
+          <t>CF_M06_P03</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1437,11 +1437,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.8250999999999999</v>
+        <v>0.825</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Decorator</t>
+          <t>Observer</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1451,25 +1451,29 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>A design pattern that allows adding behavior to an object, used to extend component functionality for testing.</t>
+          <t>Design pattern to observe the state of an object in a program, reflected in the Flux architecture where stores act as subjects.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>['P_02']</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>P_04</t>
+          <t>P_03</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Decorator Pattern</t>
+          <t>Observer Pattern</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1479,21 +1483,21 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>The decorator pattern is a design pattern that allows you to add behavior to an object, both statically and dynamically. In this project, it has been used to facilitate testing tasks.</t>
+          <t>The observer pattern is a design pattern for observing the state of an object in a program.</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>CF_M06_AU23</t>
+          <t>CF_M06_P02</t>
         </is>
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
-          <t>CF_M06_P04</t>
+          <t>CF_M06_P03</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
@@ -1501,89 +1505,85 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AU_20</t>
+          <t>P_04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CF_M06_AU28</t>
+          <t>CF_M06_P04</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.8493000000000001</v>
-      </c>
-      <c r="E6" t="inlineStr"/>
+        <v>0.8250999999999999</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Decorator</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>The Waapiti Server is the API of the company that the application consumes, responsible for communicating with the database and other services hosted on AWS.</t>
+          <t>Design pattern that allows adding behavior to an object, used to extend component functionality for testing.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>['AU_02', 'AU_05']</t>
-        </is>
-      </c>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>AU_20</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>waapiti server, data layer</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>P_04</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Decorator Pattern</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>It is the server responsible for communicating with the database and other services hosted on AWS.</t>
+          <t>The decorator pattern is a design pattern that allows you to add behavior to an object, both statically and dynamically. In this project, it has been used to facilitate testing tasks.</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>CF_M06_AU02, CF_M06_AU05</t>
+          <t>CF_M06_AU23</t>
         </is>
       </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
-          <t>CF_M06_AU28</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>waapiti server, data</t>
-        </is>
-      </c>
+          <t>CF_M06_P04</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AU_04</t>
+          <t>AU_05</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1623,7 +1623,7 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>AU_04</t>
+          <t>AU_05</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
@@ -1661,94 +1661,86 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AU_21</t>
+          <t>AU_03</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CF_M06_AU13</t>
+          <t>CF_M06_AU02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.8711</v>
-      </c>
-      <c r="E8" t="inlineStr"/>
+        <v>0.8594000000000001</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Waapiti Platform</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>The presentation layer (mobile application) communicates with the user, displaying system data and collecting user input.</t>
+          <t>Scalable, web-based platform that allows automatic distribution of content and management of players.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>['AU_03', 'AU_01']</t>
-        </is>
-      </c>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>AU_21</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>presentation layer, mobile device</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>AU_03</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Waapiti Server</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Presentation: This is the layer that communicates with the user</t>
+          <t>API [15] of the company consuming the application. It is the server responsible for communicating with the database and other services hosted on AWS.</t>
         </is>
       </c>
       <c r="P8" t="n">
         <v>45</v>
       </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>CF_M06_AU03, CF_M06_AU12</t>
-        </is>
-      </c>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
-          <t>CF_M06_AU13</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>presentation, user</t>
-        </is>
-      </c>
+          <t>CF_M06_AU02</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AU_22</t>
+          <t>AU_12</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CF_M06_AU10</t>
+          <t>CF_M06_AU28</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1757,7 +1749,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.8976</v>
+        <v>0.9087</v>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
@@ -1767,28 +1759,28 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>The Dispatcher notifies Stores when the state should be modified.</t>
+          <t>The Waapiti server communicates with the database and other services hosted on AWS.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>['AU_08', 'AU_06']</t>
+          <t>['AU_03', 'AU_06']</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>AU_22</t>
+          <t>AU_12</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>dispatcher, store</t>
+          <t>waapiti platform, data layer</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -1799,33 +1791,33 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>With the data obtained, the Dispatcher notifies the Stores that need to be modified, thus updating the components.</t>
+          <t>It is the server responsible for communicating with the database and other services hosted on AWS.</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>CF_M06_AU08, CF_M06_AU07</t>
+          <t>CF_M06_AU02, CF_M06_AU05</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
-          <t>CF_M06_AU10</t>
+          <t>CF_M06_AU28</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>action, store</t>
+          <t>waapiti server, data</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AU_19</t>
+          <t>AU_11</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1859,18 +1851,18 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>['AU_01', 'AU_02']</t>
+          <t>['AU_04', 'AU_03']</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>AU_19</t>
+          <t>AU_11</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>mobile device, waapiti server</t>
+          <t>presentation layer, waapiti platform</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -1907,12 +1899,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AU_01</t>
+          <t>AU_07</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CF_M06_AU01</t>
+          <t>CF_M06_AU06</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1921,59 +1913,67 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.9895</v>
+        <v>1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mobile Device</t>
+          <t>React Native</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Device</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>The physical device where the application is hosted, either iOS or Android.</t>
+          <t>Framework used to develop the mobile application.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>46, 51</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>['AU_04']</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>AU_01</t>
+          <t>AU_07</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Mobile device</t>
+          <t>React Native</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Device</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>This is the device where the application will be hosted.</t>
+          <t>The framework used in this work is React Native, which runs on React (a framework for creating frontend interfaces).</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>45</v>
-      </c>
-      <c r="Q11" t="inlineStr"/>
+        <v>46</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>CF_M06_AU23</t>
+        </is>
+      </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
-          <t>CF_M06_AU01</t>
+          <t>CF_M06_AU06</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
@@ -1981,12 +1981,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AU_09</t>
+          <t>AU_02</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CF_M06_AU06</t>
+          <t>CF_M06_AU24</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1999,63 +1999,56 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>React Native</t>
+          <t>Player</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Device</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Open source development framework used to develop applications for Android and iOS.</t>
+          <t>Computer equipment that acts as an intermediary between the Waapiti platform and the audiovisual support.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>['AU_03']</t>
-        </is>
-      </c>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>AU_09</t>
+          <t>AU_02</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>React Native</t>
+          <t>Player</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Device</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>The framework used in this work is React Native, which runs on React (a framework for creating frontend interfaces).</t>
+          <t xml:space="preserve">these are computer equipment that act as an intermediary between the Waapiti platform and the audiovisual media itself, thus allowing the synchronization or reproduction of client
+content. </t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>46</v>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>CF_M06_AU23</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
-          <t>CF_M06_AU06</t>
+          <t>CF_M06_AU24</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
@@ -2063,12 +2056,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AU_10</t>
+          <t>AU_16</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CF_M06_AU14</t>
+          <t>CF_M06_AU29</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2081,7 +2074,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>React</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2091,29 +2084,29 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Library for building user interfaces using Javascript.</t>
+          <t>Aquesta interactuar` a amb l’API de Waapiti mitjan¸ cant peticions HTTP.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>['AU_09']</t>
+          <t>['AU_11']</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>AU_10</t>
+          <t>AU_16</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>React</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2123,21 +2116,21 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>is a library for building user interfaces using Javascript.</t>
+          <t>This will interact with the Waapiti API using HTTP requests.</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>CF_M06_AU23</t>
+          <t>CF_M06_AU26</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
-          <t>CF_M06_AU14</t>
+          <t>CF_M06_AU29</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
@@ -2145,17 +2138,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P_05</t>
+          <t>AU_10</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CF_M06_P05</t>
+          <t>CF_M06_AU19</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -2163,59 +2156,59 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lazy Loading</t>
+          <t>NestJS</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>The concept of loading objects/components only when they are necessary.</t>
+          <t>Progressive NodeJS framework for building efficient, reliable, and scalable backend applications.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>['AU_03']</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>P_05</t>
+          <t>AU_10</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Lazy Loading</t>
+          <t>NestJS</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>The concept of Lazy Loading consists of loading objects/components only when they are needed. In this way, we achieve optimized efficiency. In this project, thanks to the React Navigation library, used to manage the application's navigation, this concept has been implemented.</t>
+          <t>is a progressive NodeJS framework for creating efficient applications reliable and scalable backend entities.</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>49</v>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>CF_M06_AU23</t>
-        </is>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
-          <t>CF_M06_P05</t>
+          <t>CF_M06_AU19</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
@@ -2228,7 +2221,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CF_M06_AU09</t>
+          <t>CF_M06_AU25</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2241,17 +2234,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dispatcher</t>
+          <t>Redux</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>The central axis that manages the entire data flow and notifies Stores when the state should be modified.</t>
+          <t>Library used to manage the application state.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2259,7 +2252,11 @@
           <t>47</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>['AU_05']</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
@@ -2269,17 +2266,17 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Dispatcher</t>
+          <t>Redux</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>This is the central hub that manages all the data flow.</t>
+          <t>Redux [19] is a library used to manage application state. It is inspired by the Flux architecture, but with a simpler implementation.</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -2287,13 +2284,13 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>CF_M06_P02</t>
+          <t>CF_M06_AU23</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
-          <t>CF_M06_AU09</t>
+          <t>CF_M06_AU25</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
@@ -2301,12 +2298,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AU_12</t>
+          <t>AU_09</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CF_M06_AU16</t>
+          <t>CF_M06_AU22</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2319,7 +2316,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Jest</t>
+          <t>AWS SNS</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2329,49 +2326,49 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Testing framework for Javascript.</t>
+          <t>Service used for the delivery of push notifications.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>['AU_13']</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>AU_12</t>
+          <t>AU_09</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Jest</t>
+          <t>AWS SNS</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>is a testing framework for Javascript. It is also the libraryrecommended for React projects. [20]</t>
+          <t>In the end it was decided to use AWS SNS due to the cost compared to Expo Push API. In addition, AWS SNS is more scalable and can be used by other services.</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>51</v>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>CF_M06_AU23</t>
-        </is>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
-          <t>CF_M06_AU16</t>
+          <t>CF_M06_AU22</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
@@ -2379,17 +2376,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AU_17</t>
+          <t>P_02</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CF_M06_AU29</t>
+          <t>CF_M06_P02</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -2397,63 +2394,59 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>Flux</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Communication protocol used by the mobile application to interact with the Waapiti API.</t>
+          <t>Architecture for managing and flowing data in a web application, designed to replace MVC.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>['AU_19']</t>
-        </is>
-      </c>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>AU_17</t>
+          <t>P_02</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>Flux</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>This will interact with the Waapiti API using HTTP requests.</t>
+          <t>In this project it has been decided to develop using the Flux architecture [18], introduced by Facebook.</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>CF_M06_AU26</t>
+          <t>CF_M06_AU23</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
-          <t>CF_M06_AU29</t>
+          <t>CF_M06_P02</t>
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
@@ -2461,12 +2454,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AU_02</t>
+          <t>AU_17</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CF_M06_AU02</t>
+          <t>CF_M06_AU31</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2479,756 +2472,66 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Waapiti Server</t>
+          <t>Socket</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>API of the company that the application consumes, responsible for communicating with the database and other services hosted on AWS.</t>
+          <t>Via sockets es poden rebre els logs en temps real [...] Aquesta funcionalitat es connecta via socket amb el servidor.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>38,70,79</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>['AU_14', 'AU_15']</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>AU_02</t>
+          <t>AU_17</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Waapiti Server</t>
+          <t>Socket</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>API [15] of the company consuming the application. It is the server responsible for communicating with the database and other services hosted on AWS.</t>
+          <t>the content according to the messages that it sends.</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>45</v>
-      </c>
-      <c r="Q18" t="inlineStr"/>
+        <v>70</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>CF_M06_AU30</t>
+        </is>
+      </c>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
-          <t>CF_M06_AU02</t>
+          <t>CF_M06_AU31</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>AU_06</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>CF_M06_AU07</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Store</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Component</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>The component that contains the state and logic of the application.</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>AU_06</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>Store</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>Component</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>This is the component that contains the state and logic of the application.</t>
-        </is>
-      </c>
-      <c r="P19" t="n">
-        <v>46</v>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>CF_M06_P02</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>CF_M06_AU07</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>AU_11</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>CF_M06_AU15</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Expo</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Open source framework for native Android, iOS and Web applications.</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>['AU_09']</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>AU_11</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>Expo</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>is an open source framework for native Android, iOS and Web applications.</t>
-        </is>
-      </c>
-      <c r="P20" t="n">
-        <v>51</v>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>CF_M06_AU23</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>CF_M06_AU15</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>AU_13</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>CF_M06_AU17</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>NodeJS</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Javascript execution environment used for compilation.</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>AU_13</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>NodeJS</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>is a Javascript runtime environment that allows you to run it outside of the browser. In this case it is used to compile.</t>
-        </is>
-      </c>
-      <c r="P21" t="n">
-        <v>51</v>
-      </c>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>CF_M06_AU17</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>AU_15</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>CF_M06_AU19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>NestJS</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Progressive NodeJS framework for creating efficient, reliable and scalable backend applications.</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>['AU_02']</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>AU_15</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>NestJS</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>is a progressive NodeJS framework for creating efficient applications reliable and scalable backend entities.</t>
-        </is>
-      </c>
-      <c r="P22" t="n">
-        <v>51</v>
-      </c>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>CF_M06_AU19</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>AU_16</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>CF_M06_AU22</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>AWS SNS</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Managed service that offers message delivery from publishers to subscribers, used for push notifications.</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>['AU_02', 'AU_23']</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>AU_16</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>AWS SNS</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>Service</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>In the end it was decided to use AWS SNS due to the cost compared to Expo Push API. In addition, AWS SNS is more scalable and can be used by other services.</t>
-        </is>
-      </c>
-      <c r="P23" t="n">
-        <v>92</v>
-      </c>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>CF_M06_AU22</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>P_02</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>CF_M06_P02</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>pattern</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Flux</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Architectural Pattern</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>An architecture for managing and flowing data in a web application, designed to replace the Model-View-Controller (MVC) pattern.</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>P_02</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>Flux</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>Architectural Pattern</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>In this project it has been decided to develop using the Flux architecture [18], introduced by Facebook.</t>
-        </is>
-      </c>
-      <c r="P24" t="n">
-        <v>46</v>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>CF_M06_AU23</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>CF_M06_P02</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>P_01</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>CF_M06_P01</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>pattern</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Three Layers</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Architectural Pattern</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>This architecture follows the 3-layer model: Presentation, Domain, and Data.</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>P_01</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>Three Layers</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>Architectural Pattern</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>This architecture follows the 3-layer model</t>
-        </is>
-      </c>
-      <c r="P25" t="n">
-        <v>45</v>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>CF_M06_AU23</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>CF_M06_P01</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>AU_07</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>CF_M06_AU08</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Component</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>A Javascript object that indicates an intention to modify the application state.</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>AU_07</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>Component</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> is a Javascript object that indicates an intention to modify the state of the application.</t>
-        </is>
-      </c>
-      <c r="P26" t="n">
-        <v>47</v>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>CF_M06_P02</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>CF_M06_AU08</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>AU_14</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>CF_M06_AU18</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>TypeScript</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Programming language developed by Microsoft, a superset of Javascript.</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>AU_14</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>TypeScript</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>it is a programming language developed and maintained by Microsoft</t>
-        </is>
-      </c>
-      <c r="P27" t="n">
-        <v>51</v>
-      </c>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>CF_M06_AU18</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3241,7 +2544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3289,7 +2592,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AU_18</t>
+          <t>AU_01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3305,7 +2608,7 @@
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Third-party companies that offer digital signage service/consulting using Waapiti technology.</t>
+          <t>Third-party companies that offer digital signage service/consultancy using Waapiti technology.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -3325,7 +2628,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AU_23</t>
+          <t>AU_13</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3336,12 +2639,12 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>mobile device, aws sns</t>
+          <t>waapiti platform, aws sns</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>The mobile application uses AWS SNS for push notifications.</t>
+          <t>The application uses AWS SNS for the delivery of push notifications.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -3355,7 +2658,75 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.86</v>
+        <v>0.8771</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AU_14</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>presentation layer, waapiti platform</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>The application uses sockets to receive logs in real time from the server.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>CF_M06_AU30</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="n">
+        <v>0.7722</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>P_01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Architectural Pattern</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>3-Layer Architecture</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>The architecture follows the 3-layer model: Presentation, Domain, and Data.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>CF_M06_P01</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Three Layers</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>0.8511</v>
       </c>
     </row>
   </sheetData>
@@ -3369,7 +2740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3417,248 +2788,251 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CF_M06_AU11</t>
+          <t>CF_M06_AU01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>dispatcher, store</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
+          <t>Device</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Mobile device</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>This is the device where the application will be hosted.</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>AU_01</t>
+          <t>AU_07</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Mobile Device</t>
+          <t>React Native</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>0.7089</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CF_M06_AU12</t>
+          <t>CF_M06_AU07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>User</t>
+          <t>Store</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>As already mentioned, there are third-party companies that offer digital signage consulting using Waapiti technology. They are end users of this project.</t>
+          <t>This is the component that contains the state and logic of the application.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AU_07</t>
+          <t>AU_01</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Action</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.7607</v>
+        <v>0.6647999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CF_M06_AU20</t>
+          <t>CF_M06_AU08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Firebase Cloud Messaging</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Firebase Cloud Messaging (FCM) for Android devices and Apple Push Notification Service (APNS) for iOS devices.</t>
+          <t xml:space="preserve"> is a Javascript object that indicates an intention to modify the state of the application.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AU_23</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>AU_02</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
       <c r="H4" t="n">
-        <v>0.6817</v>
+        <v>0.7835</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CF_M06_AU21</t>
+          <t>CF_M06_AU09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Apple Push Notification Service</t>
+          <t>Dispatcher</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Firebase Cloud Messaging (FCM) for Android devices and Apple Push Notification Service (APNS) for iOS devices.</t>
+          <t>This is the central hub that manages all the data flow.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AU_23</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>AU_01</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
       <c r="H5" t="n">
-        <v>0.8003</v>
+        <v>0.6454</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CF_M06_AU23</t>
+          <t>CF_M06_AU10</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Mobile Application</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>action, store</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>The project “Development of a mobile application for a digital signage company”</t>
+          <t>With the data obtained, the Dispatcher notifies the Stores that need to be modified, thus updating the components.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AU_01</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Mobile Device</t>
-        </is>
-      </c>
+          <t>AU_15</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>0.8665</v>
+        <v>0.6262</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CF_M06_AU24</t>
+          <t>CF_M06_AU11</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Device</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Player</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>dispatcher, store</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">these are computer equipment that act as an intermediary between the Waapiti platform and the audiovisual media itself, thus allowing the synchronization or reproduction of client
-content. </t>
+          <t>This is the central hub that manages all the data flow. It notifies the Stores when the state needs to be modified.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AU_07</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
+          <t>AU_12</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>0.7835</v>
+        <v>0.6307</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CF_M06_AU25</t>
+          <t>CF_M06_AU12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Redux</t>
+          <t>User</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Redux [19] is a library used to manage application state. It is inspired by the Flux architecture, but with a simpler implementation.</t>
+          <t>As already mentioned, there are third-party companies that offer digital signage consulting using Waapiti technology. They are end users of this project.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AU_10</t>
+          <t>AU_02</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>React</t>
+          <t>Player</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.7194</v>
+        <v>0.7565</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CF_M06_AU26</t>
+          <t>CF_M06_AU13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3669,99 +3043,411 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
+          <t>presentation, user</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Presentation: This is the layer that communicates with the user</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>AU_04</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Presentation Layer</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>0.8952</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CF_M06_AU14</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>React</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>is a library for building user interfaces using Javascript.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>AU_08</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Redux</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>0.7194</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CF_M06_AU15</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Expo</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>is an open source framework for native Android, iOS and Web applications.</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>P_03</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Observer</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>0.6337</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CF_M06_AU16</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Jest</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>is a testing framework for Javascript. It is also the libraryrecommended for React projects. [20]</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>AU_02</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>0.6353</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CF_M06_AU17</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NodeJS</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>is a Javascript runtime environment that allows you to run it outside of the browser. In this case it is used to compile.</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>AU_10</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>NestJS</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>0.744</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CF_M06_AU18</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>TypeScript</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>it is a programming language developed and maintained by Microsoft</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>AU_10</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>NestJS</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>0.6955</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CF_M06_AU20</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Firebase Cloud Messaging</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Firebase Cloud Messaging (FCM) for Android devices and Apple Push Notification Service (APNS) for iOS devices.</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>AU_13</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="n">
+        <v>0.6879</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CF_M06_AU21</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Apple Push Notification Service</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Firebase Cloud Messaging (FCM) for Android devices and Apple Push Notification Service (APNS) for iOS devices.</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>AU_13</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="n">
+        <v>0.8037</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CF_M06_AU23</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Mobile Application</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>The project “Development of a mobile application for a digital signage company”</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>AU_11</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="n">
+        <v>0.7667</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CF_M06_AU26</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
           <t>waapiti server, mobile application</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>The requirement will be understood as complete if the communications between the server and the application use the minimum possible information.
 and authenticated.</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>AU_17</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>AU_16</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
         <is>
           <t>HTTP</t>
         </is>
       </c>
-      <c r="H9" t="n">
+      <c r="H18" t="n">
         <v>0.6449</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>CF_M06_AU30</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>mobile application, waapiti server</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>This functionality connects via socket [25] with the server and displays</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>AU_17</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CF_M06_P01</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Architectural Pattern</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Three Layers</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>This architecture follows the 3-layer model</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>P_01</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>3-Layer Architecture</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>0.8511</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CF_M06_P05</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Design Pattern</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Lazy Loading</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>The concept of Lazy Loading consists of loading objects/components only when they are needed. In this way, we achieve optimized efficiency. In this project, thanks to the React Navigation library, used to manage the application's navigation, this concept has been implemented.</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>AU_16</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
         <is>
           <t>HTTP</t>
         </is>
       </c>
-      <c r="H10" t="n">
-        <v>0.6713</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>CF_M06_AU31</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Socket</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>the content according to the messages that it sends.</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>AU_07</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>0.6631</v>
+      <c r="H20" t="n">
+        <v>0.6162</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/architecture/validation/CF_M06/run_2/CF_M06_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/validation/CF_M06/run_2/CF_M06_arch_eval.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,6 +440,11 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>mean semantic meaning</t>
         </is>
       </c>
@@ -456,7 +461,10 @@
       <c r="C2" t="n">
         <v>0.4722</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="n">
+        <v>0.5965</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -475,6 +483,9 @@
         <v>0.4828</v>
       </c>
       <c r="D3" t="n">
+        <v>0.6222</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.9266</v>
       </c>
     </row>
@@ -491,6 +502,9 @@
         <v>0.4286</v>
       </c>
       <c r="D4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E4" t="n">
         <v>0.8781</v>
       </c>
     </row>
@@ -1221,14 +1235,11 @@
           <t>45</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>AU_04</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>Presentation</t>
@@ -1252,13 +1263,11 @@
           <t>CF_M06_P01</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>CF_M06_AU03</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1279,7 +1288,6 @@
       <c r="D3" t="n">
         <v>0.8071</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1300,7 +1308,6 @@
           <t>['AU_04', 'AU_03']</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>AU_15</t>
@@ -1311,7 +1318,6 @@
           <t>presentation layer, waapiti platform</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1330,7 +1336,6 @@
           <t>CF_M06_AU23, CF_M06_AU02</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>CF_M06_AU30</t>
@@ -1381,14 +1386,11 @@
           <t>45</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>AU_06</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>Data</t>
@@ -1412,13 +1414,11 @@
           <t>CF_M06_P01</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>CF_M06_AU05</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1464,13 +1464,11 @@
           <t>['P_02']</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>P_03</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>Observer Pattern</t>
@@ -1494,13 +1492,11 @@
           <t>CF_M06_P02</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>CF_M06_P03</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1541,14 +1537,11 @@
           <t>49</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>P_04</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Decorator Pattern</t>
@@ -1572,13 +1565,11 @@
           <t>CF_M06_AU23</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>CF_M06_P04</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1619,14 +1610,11 @@
           <t>45</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>AU_05</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>Domain</t>
@@ -1650,13 +1638,11 @@
           <t>CF_M06_P01</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>CF_M06_AU04</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1697,14 +1683,11 @@
           <t>9</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>AU_03</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Waapiti Server</t>
@@ -1723,14 +1706,11 @@
       <c r="P8" t="n">
         <v>45</v>
       </c>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>CF_M06_AU02</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1751,7 +1731,6 @@
       <c r="D9" t="n">
         <v>0.9087</v>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1772,7 +1751,6 @@
           <t>['AU_03', 'AU_06']</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>AU_12</t>
@@ -1783,7 +1761,6 @@
           <t>waapiti platform, data layer</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1802,7 +1779,6 @@
           <t>CF_M06_AU02, CF_M06_AU05</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>CF_M06_AU28</t>
@@ -1833,7 +1809,6 @@
       <c r="D10" t="n">
         <v>0.9185</v>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1854,7 +1829,6 @@
           <t>['AU_04', 'AU_03']</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>AU_11</t>
@@ -1865,7 +1839,6 @@
           <t>presentation layer, waapiti platform</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1884,7 +1857,6 @@
           <t>CF_M06_AU01, CF_M06_AU02</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>CF_M06_AU27</t>
@@ -1940,13 +1912,11 @@
           <t>['AU_04']</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>AU_07</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>React Native</t>
@@ -1970,13 +1940,11 @@
           <t>CF_M06_AU23</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>CF_M06_AU06</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2017,14 +1985,11 @@
           <t>9</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>AU_02</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>Player</t>
@@ -2044,14 +2009,11 @@
       <c r="P12" t="n">
         <v>9</v>
       </c>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>CF_M06_AU24</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2097,13 +2059,11 @@
           <t>['AU_11']</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>AU_16</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>HTTP</t>
@@ -2127,13 +2087,11 @@
           <t>CF_M06_AU26</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>CF_M06_AU29</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2179,13 +2137,11 @@
           <t>['AU_03']</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>AU_10</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>NestJS</t>
@@ -2204,14 +2160,11 @@
       <c r="P14" t="n">
         <v>51</v>
       </c>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>CF_M06_AU19</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2257,13 +2210,11 @@
           <t>['AU_05']</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>AU_08</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>Redux</t>
@@ -2287,13 +2238,11 @@
           <t>CF_M06_AU23</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
           <t>CF_M06_AU25</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2339,13 +2288,11 @@
           <t>['AU_13']</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>AU_09</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>AWS SNS</t>
@@ -2364,14 +2311,11 @@
       <c r="P16" t="n">
         <v>92</v>
       </c>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>CF_M06_AU22</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2412,14 +2356,11 @@
           <t>46</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>P_02</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>Flux</t>
@@ -2443,13 +2384,11 @@
           <t>CF_M06_AU23</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
           <t>CF_M06_P02</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2495,13 +2434,11 @@
           <t>['AU_14', 'AU_15']</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>AU_17</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>Socket</t>
@@ -2525,13 +2462,11 @@
           <t>CF_M06_AU30</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
           <t>CF_M06_AU31</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2605,7 +2540,6 @@
           <t>Partner</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>Third-party companies that offer digital signage service/consultancy using Waapiti technology.</t>
@@ -2636,7 +2570,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>waapiti platform, aws sns</t>
@@ -2672,7 +2605,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>presentation layer, waapiti platform</t>
@@ -2688,7 +2620,6 @@
           <t>CF_M06_AU30</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>0.7722</v>
       </c>
@@ -2709,7 +2640,6 @@
           <t>3-Layer Architecture</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>The architecture follows the 3-layer model: Presentation, Domain, and Data.</t>
@@ -2801,7 +2731,6 @@
           <t>Mobile device</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>This is the device where the application will be hosted.</t>
@@ -2837,7 +2766,6 @@
           <t>Store</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>This is the component that contains the state and logic of the application.</t>
@@ -2873,7 +2801,6 @@
           <t>Action</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t xml:space="preserve"> is a Javascript object that indicates an intention to modify the state of the application.</t>
@@ -2909,7 +2836,6 @@
           <t>Dispatcher</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>This is the central hub that manages all the data flow.</t>
@@ -2940,7 +2866,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>action, store</t>
@@ -2956,7 +2881,6 @@
           <t>AU_15</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>0.6262</v>
       </c>
@@ -2972,7 +2896,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>dispatcher, store</t>
@@ -2988,7 +2911,6 @@
           <t>AU_12</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>0.6307</v>
       </c>
@@ -3009,7 +2931,6 @@
           <t>User</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>As already mentioned, there are third-party companies that offer digital signage consulting using Waapiti technology. They are end users of this project.</t>
@@ -3040,7 +2961,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>presentation, user</t>
@@ -3081,7 +3001,6 @@
           <t>React</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>is a library for building user interfaces using Javascript.</t>
@@ -3117,7 +3036,6 @@
           <t>Expo</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>is an open source framework for native Android, iOS and Web applications.</t>
@@ -3153,7 +3071,6 @@
           <t>Jest</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>is a testing framework for Javascript. It is also the libraryrecommended for React projects. [20]</t>
@@ -3189,7 +3106,6 @@
           <t>NodeJS</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>is a Javascript runtime environment that allows you to run it outside of the browser. In this case it is used to compile.</t>
@@ -3225,7 +3141,6 @@
           <t>TypeScript</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>it is a programming language developed and maintained by Microsoft</t>
@@ -3261,7 +3176,6 @@
           <t>Firebase Cloud Messaging</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>Firebase Cloud Messaging (FCM) for Android devices and Apple Push Notification Service (APNS) for iOS devices.</t>
@@ -3272,7 +3186,6 @@
           <t>AU_13</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>0.6879</v>
       </c>
@@ -3293,7 +3206,6 @@
           <t>Apple Push Notification Service</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>Firebase Cloud Messaging (FCM) for Android devices and Apple Push Notification Service (APNS) for iOS devices.</t>
@@ -3304,7 +3216,6 @@
           <t>AU_13</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>0.8037</v>
       </c>
@@ -3325,7 +3236,6 @@
           <t>Mobile Application</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>The project “Development of a mobile application for a digital signage company”</t>
@@ -3336,7 +3246,6 @@
           <t>AU_11</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>0.7667</v>
       </c>
@@ -3352,7 +3261,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
           <t>waapiti server, mobile application</t>
@@ -3394,7 +3302,6 @@
           <t>Three Layers</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>This architecture follows the 3-layer model</t>
@@ -3430,7 +3337,6 @@
           <t>Lazy Loading</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>The concept of Lazy Loading consists of loading objects/components only when they are needed. In this way, we achieve optimized efficiency. In this project, thanks to the React Navigation library, used to manage the application's navigation, this concept has been implemented.</t>
